--- a/docs/downloads/Downsview.xlsx
+++ b/docs/downloads/Downsview.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D673"/>
+  <dimension ref="A1:D672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1051,17 +1051,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brian</t>
+          <t>Merceditsz</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Keunen</t>
+          <t>Bebar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>morrow.sheila@gmail.com</t>
+          <t>mdrcexitas.bdbar@hotmail.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2217,17 +2217,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Ray</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cao</t>
+          <t>Khang</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>raycao109@gmail.com</t>
+          <t>mkhang@beanfield.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2239,17 +2239,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Bao</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Khang</t>
+          <t>Huynh</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>mkhang@beanfield.com</t>
+          <t>deltatradersvn@gmail.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2261,19 +2261,15 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bao</t>
+          <t>Linna</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Huynh</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>deltatradersvn@gmail.com</t>
-        </is>
-      </c>
+          <t>Chang</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -2283,12 +2279,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Linna</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Chang</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -2301,12 +2297,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Kayleigh</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>DonPaul</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -2319,12 +2315,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kayleigh</t>
+          <t>Alessandro</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>DonPaul</t>
+          <t>Russo</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -2337,12 +2333,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alessandro</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Russo</t>
+          <t>Paiano</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -2355,12 +2351,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Connor</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Paiano</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -2373,12 +2369,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Connor</t>
+          <t>Owen</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -2391,12 +2387,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Owen</t>
+          <t>Mirey</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Bahar</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -2409,12 +2405,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Mirey</t>
+          <t>Royce</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bahar</t>
+          <t>K</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -2427,12 +2423,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Royce</t>
+          <t>Natanya</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>Pakes</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -2445,12 +2441,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Natanya</t>
+          <t>Rocky</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pakes</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -2463,12 +2459,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Rocky</t>
+          <t>Jemerson</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>MAMARIL</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -2481,12 +2477,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Jemerson</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MAMARIL</t>
+          <t>Pei</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -2499,12 +2495,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Jhon</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pei</t>
+          <t>Madayag</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -2517,12 +2513,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Jhon</t>
+          <t>Lincoln</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Madayag</t>
+          <t>Damota-Bourne</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -2535,12 +2531,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Lincoln</t>
+          <t>Julia</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Damota-Bourne</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -2553,12 +2549,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Julia</t>
+          <t>Zahir</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Patail</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -2571,12 +2567,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Zahir</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Patail</t>
+          <t>Tran</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -2589,12 +2585,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -2607,12 +2603,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>Iankelevic</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -2625,12 +2621,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Brandon Scott</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Iankelevic</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -2643,12 +2639,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Brandon Scott</t>
+          <t>Deyah</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Pakes</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -2661,12 +2657,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Deyah</t>
+          <t>Neon</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pakes</t>
+          <t>Omand</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -2679,12 +2675,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Neon</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Omand</t>
+          <t>Avila Alonso</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -2697,12 +2693,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Steve</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Avila Alonso</t>
+          <t>Paiano</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -2715,12 +2711,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Steve</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Paiano</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -2733,12 +2729,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Maeve</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -2751,12 +2747,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Maeve</t>
+          <t>Shayaan</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Parvaneh</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -2769,12 +2765,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Shayaan</t>
+          <t>Rhayan's fiancee</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Parvaneh</t>
+          <t>kamal</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2787,12 +2783,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Rhayan's fiancee</t>
+          <t>Asif</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>kamal</t>
+          <t>Mohamed</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2805,12 +2801,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Asif</t>
+          <t>Suzy</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mohamed</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2823,12 +2819,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Suzy</t>
+          <t>Hanzi</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Xu</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2841,12 +2837,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Hanzi</t>
+          <t>Tiago</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Xu</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2859,12 +2855,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Tiago</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Guttman</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2877,12 +2873,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Pete</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Guttman</t>
+          <t>Wright</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2895,12 +2891,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pete</t>
+          <t>Nadia</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wright</t>
+          <t>Spagnuolo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2913,12 +2909,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Nadia</t>
+          <t>Hillary</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Spagnuolo</t>
+          <t>Walsh</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2931,12 +2927,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Hillary</t>
+          <t>Cary Ann</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Walsh</t>
+          <t>Noble</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2949,12 +2945,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Cary Ann</t>
+          <t>Jacques</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Noble</t>
+          <t>Fortier</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2967,12 +2963,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Jacques</t>
+          <t>sydney</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fortier</t>
+          <t>Gang</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2985,12 +2981,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>sydney</t>
+          <t>Akio</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Gang</t>
+          <t>Choi</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -3003,12 +2999,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Akio</t>
+          <t>Paolo</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Choi</t>
+          <t>Russo</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -3021,12 +3017,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Paolo</t>
+          <t>Ted</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Russo</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -3039,12 +3035,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ted</t>
+          <t>Ryab</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -3057,12 +3053,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ryab</t>
+          <t>Archie</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Grant</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -3075,12 +3071,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Archie</t>
+          <t>Cindy</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Grant</t>
+          <t>N</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -3093,12 +3089,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Cindy</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Yang</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -3111,12 +3107,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Yang</t>
+          <t>Luu</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -3129,12 +3125,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Naiel</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Luu</t>
+          <t>Solomon</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -3147,12 +3143,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Naiel</t>
+          <t>André</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Solomon</t>
+          <t>Fernandes</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -3165,12 +3161,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>André</t>
+          <t>Calissa</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Fernandes</t>
+          <t>Ylagan</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -3183,12 +3179,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Calissa</t>
+          <t>Jingqi</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ylagan</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -3201,12 +3197,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Jingqi</t>
+          <t>Kris</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Guerrieri</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -3219,12 +3215,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Kris</t>
+          <t>Cuong</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Guerrieri</t>
+          <t>Dang</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -3237,12 +3233,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cuong</t>
+          <t>Callum</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Dang</t>
+          <t>Turner</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -3255,12 +3251,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Callum</t>
+          <t>Lich</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Turner</t>
+          <t>Le</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -3273,12 +3269,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Lich</t>
+          <t>Andreus</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Le</t>
+          <t>Spagnuolo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -3291,12 +3287,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Andreus</t>
+          <t>Julien</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Spagnuolo</t>
+          <t>Letran</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -3309,12 +3305,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Julien</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Letran</t>
+          <t>Jannetta</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -3327,12 +3323,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Erynn</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jannetta</t>
+          <t>Levy</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -3345,12 +3341,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Erynn</t>
+          <t>Tiffany</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Levy</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -3363,12 +3359,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Tiffany</t>
+          <t>Allen</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Pan</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -3381,12 +3377,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Allen</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Pan</t>
+          <t>Bolger</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -3399,12 +3395,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Raye</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Bolger</t>
+          <t>Pakes</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -3417,12 +3413,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Raye</t>
+          <t>Wendy</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Pakes</t>
+          <t>Lui</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -3435,12 +3431,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Wendy</t>
+          <t>Roger</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lui</t>
+          <t>Avila Alonso</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -3453,12 +3449,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Roger</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Avila Alonso</t>
+          <t>Jones</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -3471,12 +3467,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>parker</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Jones</t>
+          <t>mccoll</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -3489,12 +3485,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>parker</t>
+          <t>Jonathan</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>mccoll</t>
+          <t>Letran</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -3507,12 +3503,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Jonathan</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Letran</t>
+          <t>Spector</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -3525,12 +3521,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Cecile</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Spector</t>
+          <t>Casimiri</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -3543,12 +3539,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Cecile</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Casimiri</t>
+          <t>MAMARIL</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -3561,12 +3557,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Athena</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>MAMARIL</t>
+          <t>Fung</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -3579,12 +3575,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Athena</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Fung</t>
+          <t>Reid</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -3597,12 +3593,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Reid</t>
+          <t>Quevillon</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -3615,12 +3611,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Albert</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Quevillon</t>
+          <t>Du</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -3633,12 +3629,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>Campbell</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Du</t>
+          <t>Damota-Bourne</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -3651,12 +3647,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Campbell</t>
+          <t>Julian</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Damota-Bourne</t>
+          <t>Lim</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -3669,12 +3665,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Julian</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Lim</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -3687,12 +3683,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Laura</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -3705,12 +3701,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Laura</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -3723,12 +3719,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Danusha</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Ambagahawita</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -3741,12 +3737,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Danusha</t>
+          <t>Noa</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Ambagahawita</t>
+          <t>Levy</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -3759,12 +3755,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Noa</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Levy</t>
+          <t>Loa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -3777,12 +3773,12 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Loa</t>
+          <t>Ioannou</t>
         </is>
       </c>
       <c r="C168" t="inlineStr"/>
@@ -3795,12 +3791,12 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Bleema</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Ioannou</t>
+          <t>Feintuch</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
@@ -3813,12 +3809,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Bleema</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Feintuch</t>
+          <t>Lister</t>
         </is>
       </c>
       <c r="C170" t="inlineStr"/>
@@ -3831,12 +3827,12 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Lister</t>
+          <t>Hodges</t>
         </is>
       </c>
       <c r="C171" t="inlineStr"/>
@@ -3849,12 +3845,12 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Benny</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Hodges</t>
+          <t>Feintuch</t>
         </is>
       </c>
       <c r="C172" t="inlineStr"/>
@@ -3867,12 +3863,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Benny</t>
+          <t>Sebastian</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Feintuch</t>
+          <t>MAMARIL</t>
         </is>
       </c>
       <c r="C173" t="inlineStr"/>
@@ -3885,12 +3881,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>taylor</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>MAMARIL</t>
+          <t>Gang</t>
         </is>
       </c>
       <c r="C174" t="inlineStr"/>
@@ -3903,12 +3899,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>taylor</t>
+          <t>Sandy</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Gang</t>
+          <t>Ngo</t>
         </is>
       </c>
       <c r="C175" t="inlineStr"/>
@@ -3921,12 +3917,12 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sandy</t>
+          <t>Zach</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Ngo</t>
+          <t>Paiano</t>
         </is>
       </c>
       <c r="C176" t="inlineStr"/>
@@ -3939,12 +3935,12 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Zach</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Paiano</t>
+          <t>Fox</t>
         </is>
       </c>
       <c r="C177" t="inlineStr"/>
@@ -3957,7 +3953,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Charlie</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -3975,12 +3971,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Charlie</t>
+          <t>Kate</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Fox</t>
+          <t>Sherkey</t>
         </is>
       </c>
       <c r="C179" t="inlineStr"/>
@@ -3993,12 +3989,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Kate</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Sherkey</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C180" t="inlineStr"/>
@@ -4011,7 +4007,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Xavier</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4029,12 +4025,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Xavier</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Wolfish</t>
         </is>
       </c>
       <c r="C182" t="inlineStr"/>
@@ -4047,15 +4043,19 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Maria</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Wolfish</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr"/>
+          <t>Bastiampillai</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>maria.lcmg@gmail.com</t>
+        </is>
+      </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -4065,19 +4065,15 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Julie</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bastiampillai</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>maria.lcmg@gmail.com</t>
-        </is>
-      </c>
+          <t>Quach</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -4087,12 +4083,12 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Julie</t>
+          <t>Justice</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Quach</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C185" t="inlineStr"/>
@@ -4105,12 +4101,12 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Justice</t>
+          <t>Carter</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Yip</t>
         </is>
       </c>
       <c r="C186" t="inlineStr"/>
@@ -4123,7 +4119,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Carter</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4141,12 +4137,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Wojtek</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Yip</t>
+          <t>M</t>
         </is>
       </c>
       <c r="C188" t="inlineStr"/>
@@ -4159,12 +4155,12 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Wojtek</t>
+          <t>Celine</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Quach</t>
         </is>
       </c>
       <c r="C189" t="inlineStr"/>
@@ -4177,12 +4173,12 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Celine</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Quach</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="C190" t="inlineStr"/>
@@ -4195,12 +4191,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C191" t="inlineStr"/>
@@ -4213,12 +4209,12 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Zoey</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Finkelstein</t>
         </is>
       </c>
       <c r="C192" t="inlineStr"/>
@@ -4231,12 +4227,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Zoey</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Finkelstein</t>
+          <t>Eaves</t>
         </is>
       </c>
       <c r="C193" t="inlineStr"/>
@@ -4249,12 +4245,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Curtis</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Eaves</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C194" t="inlineStr"/>
@@ -4267,15 +4263,19 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Curtis</t>
+          <t>Boaz</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr"/>
+          <t>Granovsky</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>granovskyb@gmail.com</t>
+        </is>
+      </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -4285,19 +4285,15 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Boaz</t>
+          <t>Dashiell</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Granovsky</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>granovskyb@gmail.com</t>
-        </is>
-      </c>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -4307,12 +4303,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Dashiell</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Largo</t>
         </is>
       </c>
       <c r="C197" t="inlineStr"/>
@@ -4325,12 +4321,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Largo</t>
+          <t>Eaves</t>
         </is>
       </c>
       <c r="C198" t="inlineStr"/>
@@ -4343,12 +4339,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Vivienne</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Eaves</t>
+          <t>Bui</t>
         </is>
       </c>
       <c r="C199" t="inlineStr"/>
@@ -4361,12 +4357,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Vivienne</t>
+          <t>Kosei</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Bui</t>
+          <t>Yamamoto</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
@@ -4379,12 +4375,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Kosei</t>
+          <t>Maggie</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Yamamoto</t>
+          <t>Chiu</t>
         </is>
       </c>
       <c r="C201" t="inlineStr"/>
@@ -4397,12 +4393,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Maggie</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Chiu</t>
+          <t>Leaman</t>
         </is>
       </c>
       <c r="C202" t="inlineStr"/>
@@ -4415,12 +4411,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Josephine</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Leaman</t>
+          <t>Lao</t>
         </is>
       </c>
       <c r="C203" t="inlineStr"/>
@@ -4433,12 +4429,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Josephine</t>
+          <t>Shosei</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Lao</t>
+          <t>Yamamoto</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
@@ -4451,12 +4447,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Shosei</t>
+          <t>Jonah</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Yamamoto</t>
+          <t>Goodman</t>
         </is>
       </c>
       <c r="C205" t="inlineStr"/>
@@ -4469,12 +4465,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Jonah</t>
+          <t>Megan</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Goodman</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C206" t="inlineStr"/>
@@ -4487,7 +4483,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Megan</t>
+          <t>Jake</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4505,12 +4501,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Jake</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C208" t="inlineStr"/>
@@ -4523,12 +4519,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Liegh</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Largo</t>
         </is>
       </c>
       <c r="C209" t="inlineStr"/>
@@ -4541,12 +4537,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Liegh</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Largo</t>
+          <t>Yip</t>
         </is>
       </c>
       <c r="C210" t="inlineStr"/>
@@ -4559,12 +4555,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Carol</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Yip</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C211" t="inlineStr"/>
@@ -4577,12 +4573,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Carol</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Yin</t>
         </is>
       </c>
       <c r="C212" t="inlineStr"/>
@@ -4595,12 +4591,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Charles</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Yin</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C213" t="inlineStr"/>
@@ -4613,12 +4609,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Charles</t>
+          <t>Micah</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Kutty</t>
         </is>
       </c>
       <c r="C214" t="inlineStr"/>
@@ -4631,12 +4627,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Micah</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Kutty</t>
+          <t>Ganz</t>
         </is>
       </c>
       <c r="C215" t="inlineStr"/>
@@ -4649,12 +4645,12 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Ganz</t>
+          <t>Choi</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
@@ -4667,12 +4663,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Choi</t>
+          <t>Sadinsky</t>
         </is>
       </c>
       <c r="C217" t="inlineStr"/>
@@ -4685,12 +4681,12 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Sadinsky</t>
+          <t>Hoffman</t>
         </is>
       </c>
       <c r="C218" t="inlineStr"/>
@@ -4703,12 +4699,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Mikko</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Hoffman</t>
+          <t>Weinper</t>
         </is>
       </c>
       <c r="C219" t="inlineStr"/>
@@ -4721,12 +4717,12 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Mikko</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Weinper</t>
+          <t>Sin</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
@@ -4739,12 +4735,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Robbie</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Sin</t>
+          <t>Spencer</t>
         </is>
       </c>
       <c r="C221" t="inlineStr"/>
@@ -4757,12 +4753,12 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Robbie</t>
+          <t>Yancy</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Spencer</t>
+          <t>Diotalevi</t>
         </is>
       </c>
       <c r="C222" t="inlineStr"/>
@@ -4775,12 +4771,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Yancy</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Diotalevi</t>
+          <t>Lapidus</t>
         </is>
       </c>
       <c r="C223" t="inlineStr"/>
@@ -4793,12 +4789,12 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Luc</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Lapidus</t>
+          <t>Hoffman</t>
         </is>
       </c>
       <c r="C224" t="inlineStr"/>
@@ -4811,12 +4807,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Luc</t>
+          <t>Andrew E</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Hoffman</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C225" t="inlineStr"/>
@@ -4829,12 +4825,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Andrew E</t>
+          <t>Noime</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Manalo</t>
         </is>
       </c>
       <c r="C226" t="inlineStr"/>
@@ -4847,12 +4843,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Noime</t>
+          <t>Felix</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Manalo</t>
+          <t>Sacuevo</t>
         </is>
       </c>
       <c r="C227" t="inlineStr"/>
@@ -4865,12 +4861,12 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Felix</t>
+          <t>Cori</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Sacuevo</t>
+          <t>Samery</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
@@ -4883,12 +4879,12 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Cori</t>
+          <t>Michael</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Samery</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C229" t="inlineStr"/>
@@ -4901,12 +4897,12 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Malcolm</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C230" t="inlineStr"/>
@@ -4919,12 +4915,12 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Malcolm</t>
+          <t>Rufus</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Ng</t>
         </is>
       </c>
       <c r="C231" t="inlineStr"/>
@@ -4937,12 +4933,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Rufus</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ng</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
@@ -4955,12 +4951,12 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Samery</t>
         </is>
       </c>
       <c r="C233" t="inlineStr"/>
@@ -4973,12 +4969,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Khristelle</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Samery</t>
+          <t>Yap</t>
         </is>
       </c>
       <c r="C234" t="inlineStr"/>
@@ -4991,12 +4987,12 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Khristelle</t>
+          <t>Paige</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Yap</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C235" t="inlineStr"/>
@@ -5009,12 +5005,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Paige</t>
+          <t>Nigel</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Szeto</t>
         </is>
       </c>
       <c r="C236" t="inlineStr"/>
@@ -5027,12 +5023,12 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Nigel</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Szeto</t>
+          <t>Shafer</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
@@ -5045,12 +5041,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Neda</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Shafer</t>
+          <t>Galin</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
@@ -5063,12 +5059,12 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Neda</t>
+          <t>Kaya</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Galin</t>
+          <t>Weinper</t>
         </is>
       </c>
       <c r="C239" t="inlineStr"/>
@@ -5081,12 +5077,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Kaya</t>
+          <t>Katarina</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Weinper</t>
+          <t>Baljozovic</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
@@ -5099,12 +5095,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Katarina</t>
+          <t>Dan</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Baljozovic</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
@@ -5117,12 +5113,12 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Dan</t>
+          <t>Damon</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Szeto</t>
         </is>
       </c>
       <c r="C242" t="inlineStr"/>
@@ -5135,12 +5131,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Damon</t>
+          <t>Layah</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Szeto</t>
+          <t>Lapidus</t>
         </is>
       </c>
       <c r="C243" t="inlineStr"/>
@@ -5153,12 +5149,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Layah</t>
+          <t>Chloe</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Lapidus</t>
+          <t>Guttman</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
@@ -5171,12 +5167,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Chloe</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Guttman</t>
+          <t>rattner</t>
         </is>
       </c>
       <c r="C245" t="inlineStr"/>
@@ -5189,12 +5185,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>rattner</t>
+          <t>Dennis</t>
         </is>
       </c>
       <c r="C246" t="inlineStr"/>
@@ -5207,12 +5203,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Ellis</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Dennis</t>
+          <t>Sadinsky</t>
         </is>
       </c>
       <c r="C247" t="inlineStr"/>
@@ -5225,12 +5221,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Ellis</t>
+          <t>Leo</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Sadinsky</t>
+          <t>Macdonald</t>
         </is>
       </c>
       <c r="C248" t="inlineStr"/>
@@ -5243,12 +5239,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Leo</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Macdonald</t>
+          <t>Kraska</t>
         </is>
       </c>
       <c r="C249" t="inlineStr"/>
@@ -5261,12 +5257,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Jayden</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Kraska</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C250" t="inlineStr"/>
@@ -5279,12 +5275,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Jayden</t>
+          <t>Kev</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Woo</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C251" t="inlineStr"/>
@@ -5297,12 +5293,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Kev</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Kung</t>
         </is>
       </c>
       <c r="C252" t="inlineStr"/>
@@ -5315,12 +5311,12 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Joelle</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Kung</t>
+          <t>Yue</t>
         </is>
       </c>
       <c r="C253" t="inlineStr"/>
@@ -5333,12 +5329,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Joelle</t>
+          <t>Solly</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Yue</t>
+          <t>Gerb</t>
         </is>
       </c>
       <c r="C254" t="inlineStr"/>
@@ -5351,12 +5347,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Solly</t>
+          <t>Haley</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Gerb</t>
+          <t>Fry</t>
         </is>
       </c>
       <c r="C255" t="inlineStr"/>
@@ -5369,12 +5365,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Haley</t>
+          <t>Ashlee</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Fry</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
@@ -5387,12 +5383,12 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Ashlee</t>
+          <t>Emma</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Golubovic</t>
         </is>
       </c>
       <c r="C257" t="inlineStr"/>
@@ -5405,12 +5401,12 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Evan</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Golubovic</t>
+          <t>Dennis</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
@@ -5423,12 +5419,12 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Evan</t>
+          <t>Elise</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Dennis</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C259" t="inlineStr"/>
@@ -5441,12 +5437,12 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Elise</t>
+          <t>Avi</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Smith</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
@@ -5459,12 +5455,12 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Avi</t>
+          <t>William</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Smith</t>
+          <t>Bowers</t>
         </is>
       </c>
       <c r="C261" t="inlineStr"/>
@@ -5477,12 +5473,12 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Marlena</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Bowers</t>
+          <t>Wu</t>
         </is>
       </c>
       <c r="C262" t="inlineStr"/>
@@ -5495,12 +5491,12 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Marlena</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Kessler</t>
         </is>
       </c>
       <c r="C263" t="inlineStr"/>
@@ -5513,12 +5509,12 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Zarif</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Kessler</t>
+          <t>Rahman</t>
         </is>
       </c>
       <c r="C264" t="inlineStr"/>
@@ -5531,12 +5527,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Zarif</t>
+          <t>Congcong</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Rahman</t>
+          <t>Zhang</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
@@ -5549,12 +5545,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Congcong</t>
+          <t>Dezhong</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
@@ -5567,12 +5563,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Dezhong</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>Ganz</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
@@ -5585,12 +5581,12 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Aiden</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Ganz</t>
+          <t>rattner</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
@@ -5603,12 +5599,12 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Aiden</t>
+          <t>Nicolas</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>rattner</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C269" t="inlineStr"/>
@@ -5621,12 +5617,12 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Nicolas</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Sadinsky</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
@@ -5639,12 +5635,12 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Ronan</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Sadinsky</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="C271" t="inlineStr"/>
@@ -5657,12 +5653,12 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Ronan</t>
+          <t>Laurence</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chen</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
@@ -5675,12 +5671,12 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Laurence</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Chen</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
@@ -5693,12 +5689,12 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>Joy</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Ngo</t>
         </is>
       </c>
       <c r="C274" t="inlineStr"/>
@@ -5711,12 +5707,12 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Joy</t>
+          <t>Cadence</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Ngo</t>
+          <t>Beach</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
@@ -5729,12 +5725,12 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Cadence</t>
+          <t>Yasir</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>Salih</t>
         </is>
       </c>
       <c r="C276" t="inlineStr"/>
@@ -5747,12 +5743,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Yasir</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Salih</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
@@ -5765,12 +5761,12 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Cole</t>
         </is>
       </c>
       <c r="C278" t="inlineStr"/>
@@ -5783,12 +5779,12 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Gale</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Cole</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
@@ -5801,12 +5797,12 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Gale</t>
+          <t>Claudia</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Jacobson</t>
         </is>
       </c>
       <c r="C280" t="inlineStr"/>
@@ -5819,12 +5815,12 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Claudia</t>
+          <t>Sodapop</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Jacobson</t>
+          <t>Bastie</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
@@ -5837,12 +5833,12 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Sodapop</t>
+          <t>Elias</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Bastie</t>
+          <t>Allen-Kim</t>
         </is>
       </c>
       <c r="C282" t="inlineStr"/>
@@ -5855,12 +5851,12 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Elias</t>
+          <t>Michael A</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Allen-Kim</t>
+          <t>Popik</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
@@ -5873,12 +5869,12 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Michael A</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Popik</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C284" t="inlineStr"/>
@@ -5891,12 +5887,12 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Finn</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>Bastie</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
@@ -5909,12 +5905,12 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Finn</t>
+          <t>Mila</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Bastie</t>
+          <t>Jivov</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
@@ -5927,12 +5923,12 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Mila</t>
+          <t>Asha</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Jivov</t>
+          <t>singh</t>
         </is>
       </c>
       <c r="C287" t="inlineStr"/>
@@ -5945,12 +5941,12 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Asha</t>
+          <t>Ellis</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>singh</t>
+          <t>Sadinsky</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
@@ -5963,12 +5959,12 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ellis</t>
+          <t>Meera</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Sadinsky</t>
+          <t>Hofstedter</t>
         </is>
       </c>
       <c r="C289" t="inlineStr"/>
@@ -5981,12 +5977,12 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Meera</t>
+          <t>Toni</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Hofstedter</t>
+          <t>Sacuevo</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
@@ -5999,12 +5995,12 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Toni</t>
+          <t>jacob</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Sacuevo</t>
+          <t>rattner</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
@@ -6017,12 +6013,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>jacob</t>
+          <t>Margaret</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>rattner</t>
+          <t>Diotalevi</t>
         </is>
       </c>
       <c r="C292" t="inlineStr"/>
@@ -6035,12 +6031,12 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Margaret</t>
+          <t>Kevin</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Diotalevi</t>
+          <t>Gu</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
@@ -6053,12 +6049,12 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Zain</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Gu</t>
+          <t>Rahman</t>
         </is>
       </c>
       <c r="C294" t="inlineStr"/>
@@ -6071,12 +6067,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Zain</t>
+          <t>Milan</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Rahman</t>
+          <t>Baljozovic</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
@@ -6089,12 +6085,12 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Milan</t>
+          <t>Rowan</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Baljozovic</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C296" t="inlineStr"/>
@@ -6107,12 +6103,12 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Rowan</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
@@ -6130,7 +6126,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C298" t="inlineStr"/>
@@ -6143,12 +6139,12 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Ewan</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Park</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
@@ -6161,12 +6157,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ewan</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Goertz</t>
         </is>
       </c>
       <c r="C300" t="inlineStr"/>
@@ -6179,12 +6175,12 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Goertz</t>
+          <t>Ganz</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
@@ -6197,12 +6193,12 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>willow</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Ganz</t>
+          <t>wiley</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
@@ -6215,12 +6211,12 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>willow</t>
+          <t>Laila</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>wiley</t>
+          <t>Shah</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
@@ -6233,12 +6229,12 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Laila</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Shah</t>
+          <t>Nachimovitch</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
@@ -6251,15 +6247,19 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Tom</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Nachimovitch</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr"/>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>tomminhnguyen01@gmail.com</t>
+        </is>
+      </c>
       <c r="D305" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6269,19 +6269,15 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Tom</t>
+          <t>Manisha</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="C306" t="inlineStr">
-        <is>
-          <t>tomminhnguyen01@gmail.com</t>
-        </is>
-      </c>
+          <t>Sharma</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6291,12 +6287,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Manisha</t>
+          <t>Zachary</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Sharma</t>
+          <t>Mandel</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
@@ -6309,12 +6305,12 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Zachary</t>
+          <t>Niki</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Mandel</t>
+          <t>Kinsella</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
@@ -6327,12 +6323,12 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Niki</t>
+          <t>Dyllan</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Kinsella</t>
+          <t>Opinaldo</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
@@ -6345,12 +6341,12 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Dyllan</t>
+          <t>Ian C</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Opinaldo</t>
+          <t>Chow</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
@@ -6363,12 +6359,12 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Ian C</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Jessica Goldberg</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
@@ -6381,12 +6377,12 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Ari</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Jessica Goldberg</t>
+          <t>Goldberg</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
@@ -6399,12 +6395,12 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Ari</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Goldberg</t>
+          <t>Mandel</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
@@ -6417,15 +6413,19 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Mandel</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr"/>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>laurenroserd@gmail.com</t>
+        </is>
+      </c>
       <c r="D314" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6435,19 +6435,15 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Dieu</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Rose</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr">
-        <is>
-          <t>laurenroserd@gmail.com</t>
-        </is>
-      </c>
+          <t>Tran</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6457,12 +6453,12 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Dieu</t>
+          <t>Mia</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Tran</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="C316" t="inlineStr"/>
@@ -6475,12 +6471,12 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Harley</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Yee</t>
         </is>
       </c>
       <c r="C317" t="inlineStr"/>
@@ -6493,15 +6489,19 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Harley</t>
+          <t>Shazad</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Yee</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr"/>
+          <t>Suchit</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>a1biochemboi@gmail.com</t>
+        </is>
+      </c>
       <c r="D318" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6511,19 +6511,15 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Shazad</t>
+          <t>Brent</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Suchit</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr">
-        <is>
-          <t>a1biochemboi@gmail.com</t>
-        </is>
-      </c>
+          <t>Reuter</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6533,7 +6529,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Brent</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -6551,12 +6547,12 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Einat</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Levi-Israeli</t>
         </is>
       </c>
       <c r="C321" t="inlineStr"/>
@@ -6569,12 +6565,12 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Einat</t>
+          <t>Lainey</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Levi-Israeli</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C322" t="inlineStr"/>
@@ -6587,12 +6583,12 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Lainey</t>
+          <t>Sruli</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Katz</t>
         </is>
       </c>
       <c r="C323" t="inlineStr"/>
@@ -6605,7 +6601,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Sruli</t>
+          <t>Tova</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -6623,12 +6619,12 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Tova</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Katz</t>
+          <t>O'Connor</t>
         </is>
       </c>
       <c r="C325" t="inlineStr"/>
@@ -6641,12 +6637,12 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>O'Connor</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C326" t="inlineStr"/>
@@ -6659,12 +6655,12 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Nechemya</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Moskoff</t>
         </is>
       </c>
       <c r="C327" t="inlineStr"/>
@@ -6677,12 +6673,12 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Nechemya</t>
+          <t>Reuben</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Moskoff</t>
+          <t>sidlofsky</t>
         </is>
       </c>
       <c r="C328" t="inlineStr"/>
@@ -6695,12 +6691,12 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Reuben</t>
+          <t>Avigayil</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>sidlofsky</t>
+          <t>Moskoff</t>
         </is>
       </c>
       <c r="C329" t="inlineStr"/>
@@ -6713,12 +6709,12 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Avigayil</t>
+          <t>Zevi</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Moskoff</t>
+          <t>Katz</t>
         </is>
       </c>
       <c r="C330" t="inlineStr"/>
@@ -6731,7 +6727,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Zevi</t>
+          <t>Dovi</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -6749,12 +6745,12 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Dovi</t>
+          <t>Elisha</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Katz</t>
+          <t>Moskoff</t>
         </is>
       </c>
       <c r="C332" t="inlineStr"/>
@@ -6767,12 +6763,12 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Elisha</t>
+          <t>Malek</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Moskoff</t>
+          <t>Sha</t>
         </is>
       </c>
       <c r="C333" t="inlineStr"/>
@@ -6785,12 +6781,12 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Malek</t>
+          <t>Viji</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Sha</t>
+          <t>Shanthikumar</t>
         </is>
       </c>
       <c r="C334" t="inlineStr"/>
@@ -6803,12 +6799,12 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Viji</t>
+          <t>Addy</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Shanthikumar</t>
+          <t>Reuter</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
@@ -6821,12 +6817,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Addy</t>
+          <t>Yaakov</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Reuter</t>
+          <t>Katz</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
@@ -6839,15 +6835,19 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Yaakov</t>
+          <t>Adrian</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Katz</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr"/>
+          <t>Man</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>jnny_mn@yahoo.com</t>
+        </is>
+      </c>
       <c r="D337" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6857,19 +6857,15 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Adrian</t>
+          <t>Lyla</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Man</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>jnny_mn@yahoo.com</t>
-        </is>
-      </c>
+          <t>Shedletsky</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -6879,12 +6875,12 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Lyla</t>
+          <t>Masyn</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Shedletsky</t>
+          <t>Hoffman</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
@@ -6897,12 +6893,12 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Masyn</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Hoffman</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
@@ -6915,7 +6911,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Minh Q</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -6933,12 +6929,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Minh Q</t>
+          <t>Carmella</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Ylagan</t>
         </is>
       </c>
       <c r="C342" t="inlineStr"/>
@@ -6951,12 +6947,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Carmella</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Ylagan</t>
+          <t>Hoffman</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
@@ -6969,12 +6965,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Nicholas</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Hoffman</t>
+          <t>Schuldt</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
@@ -6987,7 +6983,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Nicholas</t>
+          <t>Margot</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7005,12 +7001,12 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Margot</t>
+          <t>Christina</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Schuldt</t>
+          <t>Sav</t>
         </is>
       </c>
       <c r="C346" t="inlineStr"/>
@@ -7023,12 +7019,12 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Christina</t>
+          <t>Cecilia</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Sav</t>
+          <t>Santos Pimentel</t>
         </is>
       </c>
       <c r="C347" t="inlineStr"/>
@@ -7041,12 +7037,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Cecilia</t>
+          <t>Christian</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Santos Pimentel</t>
+          <t>Schuldt</t>
         </is>
       </c>
       <c r="C348" t="inlineStr"/>
@@ -7059,12 +7055,12 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Christian</t>
+          <t>Kin</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Schuldt</t>
+          <t>Dang</t>
         </is>
       </c>
       <c r="C349" t="inlineStr"/>
@@ -7077,12 +7073,12 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Kin</t>
+          <t>Nolan</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Dang</t>
+          <t>Connolly</t>
         </is>
       </c>
       <c r="C350" t="inlineStr"/>
@@ -7095,12 +7091,12 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Nolan</t>
+          <t>Mackenzie</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Connolly</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -7113,15 +7109,19 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Mackenzie</t>
+          <t>Panza</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Tan</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>panzalee777@gmail.com</t>
+        </is>
+      </c>
       <c r="D352" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7131,17 +7131,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Panza</t>
+          <t>Lok Ting</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Cheung</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>panzalee777@gmail.com</t>
+          <t>jcltcan@gmail.com</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -7153,19 +7153,15 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Lok Ting</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Cheung</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>jcltcan@gmail.com</t>
-        </is>
-      </c>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7175,15 +7171,19 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Tarique</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Yang</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr"/>
+          <t>Al-Ansari</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>tarique24@gmail.com</t>
+        </is>
+      </c>
       <c r="D355" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7193,19 +7193,15 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Tarique</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Al-Ansari</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>tarique24@gmail.com</t>
-        </is>
-      </c>
+          <t>Luc</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7215,15 +7211,19 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Amy</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Luc</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr"/>
+          <t>Zhang</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>henryamywedding@gmail.com</t>
+        </is>
+      </c>
       <c r="D357" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7233,17 +7233,17 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Amy</t>
+          <t>Salah</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Zhang</t>
+          <t>Shar</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>henryamywedding@gmail.com</t>
+          <t>sshharih@rogers.com</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -7255,19 +7255,15 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Salah</t>
+          <t>Maya</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Shar</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>sshharih@rogers.com</t>
-        </is>
-      </c>
+          <t>Gavriel</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr"/>
       <c r="D359" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7277,15 +7273,19 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Don</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Gavriel</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr"/>
+          <t>Blackwood</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>xxpacd@hotmail.com</t>
+        </is>
+      </c>
       <c r="D360" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7295,19 +7295,15 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Don</t>
+          <t>Ann</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Blackwood</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>xxpacd@hotmail.com</t>
-        </is>
-      </c>
+          <t>Carino</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7317,15 +7313,19 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ann</t>
+          <t>Debbie</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Carino</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>d_ponte@hotmail.com</t>
+        </is>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7335,19 +7335,15 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Debbie</t>
+          <t>sdf</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>d_ponte@hotmail.com</t>
-        </is>
-      </c>
+          <t>Sheraly</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7357,12 +7353,12 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>sdf</t>
+          <t>Dawn</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Sheraly</t>
+          <t>Lewis</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -7375,12 +7371,12 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Dawn</t>
+          <t>Talia</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Lewis</t>
+          <t>Gavriel</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
@@ -7393,12 +7389,12 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Talia</t>
+          <t>Tuan</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Gavriel</t>
+          <t>Huynh</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
@@ -7411,12 +7407,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Tuan</t>
+          <t>Jerome</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Huynh</t>
+          <t>Brunel</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
@@ -7429,12 +7425,12 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Jerome</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Brunel</t>
+          <t>Fenwick</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
@@ -7447,12 +7443,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Neil</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Fenwick</t>
+          <t>Smiley</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
@@ -7465,12 +7461,12 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Neil</t>
+          <t>Tammie</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Smiley</t>
+          <t>Fong</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
@@ -7483,12 +7479,12 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Tammie</t>
+          <t>James</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Fong</t>
+          <t>Fenwick</t>
         </is>
       </c>
       <c r="C371" t="inlineStr"/>
@@ -7501,12 +7497,12 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Sean</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Fenwick</t>
+          <t>Orr</t>
         </is>
       </c>
       <c r="C372" t="inlineStr"/>
@@ -7519,12 +7515,12 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Sean</t>
+          <t>kiyan</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Orr</t>
+          <t>singh</t>
         </is>
       </c>
       <c r="C373" t="inlineStr"/>
@@ -7537,7 +7533,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>kiyan</t>
+          <t>raeya</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -7555,12 +7551,12 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>raeya</t>
+          <t>Marty</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>singh</t>
+          <t>Juravsky</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
@@ -7573,12 +7569,12 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Marty</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Juravsky</t>
+          <t>Orr</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
@@ -7591,12 +7587,12 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Orr</t>
+          <t>Leonardo</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
@@ -7609,12 +7605,12 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Alexandra</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Leonardo</t>
+          <t>Orr</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
@@ -7627,12 +7623,12 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Alexandra</t>
+          <t>Alysa</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Orr</t>
+          <t>Leung</t>
         </is>
       </c>
       <c r="C379" t="inlineStr"/>
@@ -7645,12 +7641,12 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Alysa</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Leung</t>
+          <t>Fry</t>
         </is>
       </c>
       <c r="C380" t="inlineStr"/>
@@ -7663,15 +7659,19 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Joanna</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Fry</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
+          <t>Rossa</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>p.ileggi@gmail.com</t>
+        </is>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7681,19 +7681,15 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Sung Jae</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Rossa</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>p.ileggi@gmail.com</t>
-        </is>
-      </c>
+          <t>Park</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7703,15 +7699,19 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Sung Jae</t>
+          <t>Gloria</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Park</t>
-        </is>
-      </c>
-      <c r="C383" t="inlineStr"/>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>missglorialee@gmail.com</t>
+        </is>
+      </c>
       <c r="D383" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7721,19 +7721,15 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Gloria</t>
+          <t>Karis</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C384" t="inlineStr">
-        <is>
-          <t>missglorialee@gmail.com</t>
-        </is>
-      </c>
+          <t>Wu</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7743,12 +7739,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Karis</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="C385" t="inlineStr"/>
@@ -7761,12 +7757,12 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Remy</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Mathuria</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
@@ -7779,12 +7775,12 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Remy</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Mathuria</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C387" t="inlineStr"/>
@@ -7797,12 +7793,12 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Johanna</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>Paylaga</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
@@ -7815,12 +7811,12 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Johanna</t>
+          <t>Nicky</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Paylaga</t>
+          <t>Palladino</t>
         </is>
       </c>
       <c r="C389" t="inlineStr"/>
@@ -7833,12 +7829,12 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Nicky</t>
+          <t>Rayaan</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Palladino</t>
+          <t>brijlani</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
@@ -7851,12 +7847,12 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Rayaan</t>
+          <t>Milad</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>brijlani</t>
+          <t>Modir</t>
         </is>
       </c>
       <c r="C391" t="inlineStr"/>
@@ -7869,12 +7865,12 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Milad</t>
+          <t>Ginnie</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Modir</t>
+          <t>Yeung</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
@@ -7887,12 +7883,12 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ginnie</t>
+          <t>Gerald</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Yeung</t>
+          <t>Tabil</t>
         </is>
       </c>
       <c r="C393" t="inlineStr"/>
@@ -7905,12 +7901,12 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Gerald</t>
+          <t>Kathlyn</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Tabil</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C394" t="inlineStr"/>
@@ -7923,12 +7919,12 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Kathlyn</t>
+          <t>Vincent</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C395" t="inlineStr"/>
@@ -7941,15 +7937,19 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Vincent</t>
+          <t>lexi</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Kim</t>
-        </is>
-      </c>
-      <c r="C396" t="inlineStr"/>
+          <t>gottlieb</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>lgottlieb01@rogers.com</t>
+        </is>
+      </c>
       <c r="D396" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7959,19 +7959,15 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>lexi</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>gottlieb</t>
-        </is>
-      </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>lgottlieb01@rogers.com</t>
-        </is>
-      </c>
+          <t>Wu</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -7981,12 +7977,12 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Wu</t>
+          <t>Miraples</t>
         </is>
       </c>
       <c r="C398" t="inlineStr"/>
@@ -7999,12 +7995,12 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Sunhan</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Miraples</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
@@ -8017,12 +8013,12 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Sunhan</t>
+          <t>Annika</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C400" t="inlineStr"/>
@@ -8035,12 +8031,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Annika</t>
+          <t>Gilbert</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Miraples</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
@@ -8053,12 +8049,12 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Gilbert</t>
+          <t>Liza</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Miraples</t>
+          <t>Na</t>
         </is>
       </c>
       <c r="C402" t="inlineStr"/>
@@ -8071,12 +8067,12 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Liza</t>
+          <t>Jeslyn</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Na</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
@@ -8089,12 +8085,12 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Jeslyn</t>
+          <t>Sedona</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C404" t="inlineStr"/>
@@ -8107,12 +8103,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Sedona</t>
+          <t>Ada</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
@@ -8125,12 +8121,12 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Ada</t>
+          <t>cole</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Chong</t>
         </is>
       </c>
       <c r="C406" t="inlineStr"/>
@@ -8143,12 +8139,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>cole</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Chong</t>
+          <t>Lo</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
@@ -8161,12 +8157,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Vivian</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Lo</t>
+          <t>Trinh</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
@@ -8179,12 +8175,12 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Vivian</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Trinh</t>
+          <t>BJ</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
@@ -8197,12 +8193,12 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>BJ</t>
+          <t>Miraples</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
@@ -8215,12 +8211,12 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Ranbir</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Miraples</t>
+          <t>Brar</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
@@ -8233,12 +8229,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Ranbir</t>
+          <t>Bernard</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Brar</t>
+          <t>Yung</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
@@ -8251,12 +8247,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Bernard</t>
+          <t>Sakura</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Yung</t>
+          <t>Shimada</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
@@ -8269,12 +8265,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Sakura</t>
+          <t>Oliver</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Shimada</t>
+          <t>Ter Hofstede</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
@@ -8287,12 +8283,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Oliver</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Ter Hofstede</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
@@ -8305,12 +8301,12 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Tin</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
@@ -8323,12 +8319,12 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Tin</t>
+          <t>Elad</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Winkler</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
@@ -8341,12 +8337,12 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Elad</t>
+          <t>Zev</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Winkler</t>
+          <t>Desa</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
@@ -8359,12 +8355,12 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Zev</t>
+          <t>Darryl</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Desa</t>
+          <t>Chin</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
@@ -8377,12 +8373,12 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Darryl</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Chin</t>
+          <t>jones</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
@@ -8395,12 +8391,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>OJ</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>jones</t>
+          <t>Cooperberg</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
@@ -8413,12 +8409,12 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>OJ</t>
+          <t>Drake</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Cooperberg</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
@@ -8431,12 +8427,12 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Drake</t>
+          <t>Dylan</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Beri</t>
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
@@ -8449,7 +8445,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Dylan</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -8467,12 +8463,12 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Gila</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Beri</t>
+          <t>Kohen Rydlewicz</t>
         </is>
       </c>
       <c r="C425" t="inlineStr"/>
@@ -8485,12 +8481,12 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Gila</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Kohen Rydlewicz</t>
+          <t>Ho</t>
         </is>
       </c>
       <c r="C426" t="inlineStr"/>
@@ -8503,12 +8499,12 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Cynthia</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Ho</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
@@ -8521,12 +8517,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Cynthia</t>
+          <t>Dario</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Jamalzadeh</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
@@ -8539,15 +8535,19 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Dario</t>
+          <t>Salomon</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Jamalzadeh</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr"/>
+          <t>Nezry</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>soliny44@gmail.com</t>
+        </is>
+      </c>
       <c r="D429" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -8557,19 +8557,15 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Salomon</t>
+          <t>Hendrik</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Nezry</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>soliny44@gmail.com</t>
-        </is>
-      </c>
+          <t>VanderMeulen</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr"/>
       <c r="D430" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -8579,12 +8575,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Hendrik</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>VanderMeulen</t>
+          <t>Krofchick</t>
         </is>
       </c>
       <c r="C431" t="inlineStr"/>
@@ -8597,7 +8593,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Bash</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -8615,12 +8611,12 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Bash</t>
+          <t>Josiah</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Krofchick</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C433" t="inlineStr"/>
@@ -8633,7 +8629,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Josiah</t>
+          <t>Justus</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -8651,12 +8647,12 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Justus</t>
+          <t>STEVEN</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C435" t="inlineStr"/>
@@ -8669,12 +8665,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>STEVEN</t>
+          <t>Sienna</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Subrata Da Silva</t>
         </is>
       </c>
       <c r="C436" t="inlineStr"/>
@@ -8687,12 +8683,12 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Sienna</t>
+          <t>Esther</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Subrata Da Silva</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C437" t="inlineStr"/>
@@ -8705,12 +8701,12 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Esther</t>
+          <t>Judy</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>L</t>
         </is>
       </c>
       <c r="C438" t="inlineStr"/>
@@ -8723,12 +8719,12 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Judy</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="C439" t="inlineStr"/>
@@ -8741,12 +8737,12 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Rob</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>De Luca</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
@@ -8759,12 +8755,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Rob</t>
+          <t>Chanie</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>De Luca</t>
+          <t>Yucor</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
@@ -8777,12 +8773,12 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Chanie</t>
+          <t>Kenneth</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Yucor</t>
+          <t>Vu</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
@@ -8795,12 +8791,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Kenneth</t>
+          <t>Giovanni</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Vu</t>
+          <t>De Luca</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
@@ -8813,12 +8809,12 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Giovanni</t>
+          <t>Drew</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>De Luca</t>
+          <t>Eichler</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
@@ -8831,12 +8827,12 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Drew</t>
+          <t>Antoinette</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Eichler</t>
+          <t>Anoos</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
@@ -8849,12 +8845,12 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Antoinette</t>
+          <t>Serafina</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Anoos</t>
+          <t>De Luca</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
@@ -8867,12 +8863,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Serafina</t>
+          <t>Emil</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>De Luca</t>
+          <t>Ibarra</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
@@ -8885,12 +8881,12 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Emil</t>
+          <t>Avery</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Ibarra</t>
+          <t>Weinberg</t>
         </is>
       </c>
       <c r="C448" t="inlineStr"/>
@@ -8903,12 +8899,12 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Avery</t>
+          <t>Eli</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Weinberg</t>
+          <t>Anoos</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
@@ -8921,12 +8917,12 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Eli</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Anoos</t>
+          <t>Dorneval</t>
         </is>
       </c>
       <c r="C450" t="inlineStr"/>
@@ -8939,12 +8935,12 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>Ben</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Dorneval</t>
+          <t>Weinberg</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
@@ -8962,7 +8958,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Weinberg</t>
+          <t>Kishchuk</t>
         </is>
       </c>
       <c r="C452" t="inlineStr"/>
@@ -8975,12 +8971,12 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Ben</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Kishchuk</t>
+          <t>Lau</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
@@ -8993,12 +8989,12 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Lau</t>
+          <t>Ta</t>
         </is>
       </c>
       <c r="C454" t="inlineStr"/>
@@ -9011,7 +9007,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -9029,12 +9025,12 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Ta</t>
+          <t>Lau</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
@@ -9047,15 +9043,19 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Rania</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Lau</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr"/>
+          <t>Llewellyn</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>raniallewellyn@gmail.com</t>
+        </is>
+      </c>
       <c r="D457" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9065,19 +9065,15 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Llewellyn</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>raniallewellyn@gmail.com</t>
-        </is>
-      </c>
+          <t>Bastie</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9087,12 +9083,12 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Bastie</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
@@ -9105,12 +9101,12 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Rawlins</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
@@ -9123,12 +9119,12 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Calista</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Rawlins</t>
+          <t>Fara-on</t>
         </is>
       </c>
       <c r="C461" t="inlineStr"/>
@@ -9141,7 +9137,7 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Calista</t>
+          <t>Emeniano</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -9159,12 +9155,12 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Emeniano</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Fara-on</t>
+          <t>Chang</t>
         </is>
       </c>
       <c r="C463" t="inlineStr"/>
@@ -9177,12 +9173,12 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Chang</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
@@ -9195,12 +9191,12 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
@@ -9213,12 +9209,12 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Scott</t>
         </is>
       </c>
       <c r="C466" t="inlineStr"/>
@@ -9231,12 +9227,12 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Logan</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Scott</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C467" t="inlineStr"/>
@@ -9249,15 +9245,19 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Logan</t>
+          <t>Gabriela</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Wong</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr"/>
+          <t>Kis</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>gabriela.kis@fsresidential.com</t>
+        </is>
+      </c>
       <c r="D468" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9267,19 +9267,15 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Joshua</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Kis</t>
-        </is>
-      </c>
-      <c r="C469" t="inlineStr">
-        <is>
-          <t>gabriela.kis@fsresidential.com</t>
-        </is>
-      </c>
+          <t>Abuan</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9289,15 +9285,19 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Joshua</t>
+          <t>Mateo</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Abuan</t>
-        </is>
-      </c>
-      <c r="C470" t="inlineStr"/>
+          <t>Dhoska</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>mdhoska@bflcanada.ca</t>
+        </is>
+      </c>
       <c r="D470" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9307,19 +9307,15 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Mateo</t>
+          <t>Zoya</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Dhoska</t>
-        </is>
-      </c>
-      <c r="C471" t="inlineStr">
-        <is>
-          <t>mdhoska@bflcanada.ca</t>
-        </is>
-      </c>
+          <t>Diachenko</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9329,12 +9325,12 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Zoya</t>
+          <t>Lovely Ruth</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Diachenko</t>
+          <t>Sagaoinit</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
@@ -9347,12 +9343,12 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>Lovely Ruth</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Sagaoinit</t>
+          <t>Cha</t>
         </is>
       </c>
       <c r="C473" t="inlineStr"/>
@@ -9365,15 +9361,19 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Cha</t>
-        </is>
-      </c>
-      <c r="C474" t="inlineStr"/>
+          <t>DU BELLAY</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>daniel.dubellay@gmail.com</t>
+        </is>
+      </c>
       <c r="D474" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9383,7 +9383,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Elisabeth</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -9391,11 +9391,7 @@
           <t>DU BELLAY</t>
         </is>
       </c>
-      <c r="C475" t="inlineStr">
-        <is>
-          <t>daniel.dubellay@gmail.com</t>
-        </is>
-      </c>
+      <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9405,12 +9401,12 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Elisabeth</t>
+          <t>Thai</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>DU BELLAY</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
@@ -9423,15 +9419,19 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Thai</t>
+          <t>Cassie</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Lee</t>
-        </is>
-      </c>
-      <c r="C477" t="inlineStr"/>
+          <t>Wang</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>casstre1240@gmail.com</t>
+        </is>
+      </c>
       <c r="D477" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9441,19 +9441,15 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Cassie</t>
+          <t>Teagan</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>Wang</t>
-        </is>
-      </c>
-      <c r="C478" t="inlineStr">
-        <is>
-          <t>casstre1240@gmail.com</t>
-        </is>
-      </c>
+          <t>Lee</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -9463,12 +9459,12 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Teagan</t>
+          <t>Anne-Marie</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>DU BELLAY</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
@@ -9481,12 +9477,12 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Anne-Marie</t>
+          <t>Miles</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>DU BELLAY</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
@@ -9499,12 +9495,12 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Miles</t>
+          <t>Crispin</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Almaria</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
@@ -9517,12 +9513,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Crispin</t>
+          <t>Jack</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>Almaria</t>
+          <t>Tushinski</t>
         </is>
       </c>
       <c r="C482" t="inlineStr"/>
@@ -9535,12 +9531,12 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Jack</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Tushinski</t>
+          <t>Almaria</t>
         </is>
       </c>
       <c r="C483" t="inlineStr"/>
@@ -9553,7 +9549,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Jeremiah</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -9571,12 +9567,12 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Jeremiah</t>
+          <t>koby</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Almaria</t>
+          <t>Wasel</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
@@ -9589,12 +9585,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>koby</t>
+          <t>Aaron</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>Wasel</t>
+          <t>Shulman</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
@@ -9607,12 +9603,12 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Aaron</t>
+          <t>Michela</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>Shulman</t>
+          <t>Arnone</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
@@ -9625,12 +9621,12 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Michela</t>
+          <t>Lev</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>Arnone</t>
+          <t>Gelbaum</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
@@ -9643,12 +9639,12 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Lev</t>
+          <t>George</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Gelbaum</t>
+          <t>Klar</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
@@ -9661,12 +9657,12 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>Christine</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Klar</t>
+          <t>Nhan</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
@@ -9679,12 +9675,12 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Christine</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>Nhan</t>
+          <t>Sablov</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
@@ -9697,12 +9693,12 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>Sablov</t>
+          <t>Woo</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
@@ -9715,12 +9711,12 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>Woo</t>
+          <t>Cummings</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
@@ -9733,12 +9729,12 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Travis</t>
+          <t>Nathan</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Cummings</t>
+          <t>Petrenko</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
@@ -9751,12 +9747,12 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Nathan</t>
+          <t>Valen</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>Petrenko</t>
+          <t>Sen</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
@@ -9787,12 +9783,12 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Valen</t>
+          <t>hudson</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>Sen</t>
+          <t>abrams</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
@@ -9805,12 +9801,12 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>hudson</t>
+          <t>Karen</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>abrams</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
@@ -9823,12 +9819,12 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Karen</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Kennedy</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
@@ -9841,12 +9837,12 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Evelyn</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>Kennedy</t>
+          <t>Oulahen</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
@@ -9859,12 +9855,12 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Oulahen</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
@@ -9877,12 +9873,12 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Hansen</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Yee</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
@@ -9895,12 +9891,12 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Hansen</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Yee</t>
+          <t>Singh</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
@@ -9913,12 +9909,12 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Singh</t>
+          <t>Trinh</t>
         </is>
       </c>
       <c r="C504" t="inlineStr"/>
@@ -9931,12 +9927,12 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Reya</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Trinh</t>
+          <t>Arora</t>
         </is>
       </c>
       <c r="C505" t="inlineStr"/>
@@ -9949,12 +9945,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Reya</t>
+          <t>Sahar</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Arora</t>
+          <t>Bawania</t>
         </is>
       </c>
       <c r="C506" t="inlineStr"/>
@@ -9967,12 +9963,12 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Sahar</t>
+          <t>Geoff</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>Bawania</t>
+          <t>Anderton</t>
         </is>
       </c>
       <c r="C507" t="inlineStr"/>
@@ -9985,12 +9981,12 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Geoff</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>Anderton</t>
+          <t>Sapra</t>
         </is>
       </c>
       <c r="C508" t="inlineStr"/>
@@ -10003,12 +9999,12 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Clara</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>Sapra</t>
+          <t>Wong</t>
         </is>
       </c>
       <c r="C509" t="inlineStr"/>
@@ -10021,7 +10017,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Clara</t>
+          <t>Betty</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -10039,12 +10035,12 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Betty</t>
+          <t>Hayden</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Yee</t>
         </is>
       </c>
       <c r="C511" t="inlineStr"/>
@@ -10057,12 +10053,12 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Hayden</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Yee</t>
+          <t>Chu</t>
         </is>
       </c>
       <c r="C512" t="inlineStr"/>
@@ -10075,12 +10071,12 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>zev</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Chu</t>
+          <t>Wasel</t>
         </is>
       </c>
       <c r="C513" t="inlineStr"/>
@@ -10093,12 +10089,12 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>zev</t>
+          <t>David</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>Wasel</t>
+          <t>Goodhue</t>
         </is>
       </c>
       <c r="C514" t="inlineStr"/>
@@ -10111,12 +10107,12 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Teddy</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>Goodhue</t>
+          <t>Gibson</t>
         </is>
       </c>
       <c r="C515" t="inlineStr"/>
@@ -10129,12 +10125,12 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Teddy</t>
+          <t>Derek</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>Gibson</t>
+          <t>Munroe</t>
         </is>
       </c>
       <c r="C516" t="inlineStr"/>
@@ -10147,12 +10143,12 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Derek</t>
+          <t>Keira</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Munroe</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="C517" t="inlineStr"/>
@@ -10165,12 +10161,12 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Keira</t>
+          <t>Ari</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Freiman</t>
         </is>
       </c>
       <c r="C518" t="inlineStr"/>
@@ -10183,12 +10179,12 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>Ari</t>
+          <t>Tejas</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Freiman</t>
+          <t>Raybardhan</t>
         </is>
       </c>
       <c r="C519" t="inlineStr"/>
@@ -10201,12 +10197,12 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Tejas</t>
+          <t>Mackenzie</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Raybardhan</t>
+          <t>Purkis</t>
         </is>
       </c>
       <c r="C520" t="inlineStr"/>
@@ -10219,12 +10215,12 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>Mackenzie</t>
+          <t>Sophie</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>Purkis</t>
+          <t>Oulahen</t>
         </is>
       </c>
       <c r="C521" t="inlineStr"/>
@@ -10237,12 +10233,12 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Sophie</t>
+          <t>Zaira</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>Oulahen</t>
+          <t>Bawania</t>
         </is>
       </c>
       <c r="C522" t="inlineStr"/>
@@ -10255,12 +10251,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Zaira</t>
+          <t>Myles</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Bawania</t>
+          <t>Romero</t>
         </is>
       </c>
       <c r="C523" t="inlineStr"/>
@@ -10273,12 +10269,12 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Myles</t>
+          <t>Mae</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Romero</t>
+          <t>Chong</t>
         </is>
       </c>
       <c r="C524" t="inlineStr"/>
@@ -10291,12 +10287,12 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Mae</t>
+          <t>Aarya</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Chong</t>
+          <t>Chandgothia</t>
         </is>
       </c>
       <c r="C525" t="inlineStr"/>
@@ -10309,12 +10305,12 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Aarya</t>
+          <t>Ezra</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>Chandgothia</t>
+          <t>Lombardo</t>
         </is>
       </c>
       <c r="C526" t="inlineStr"/>
@@ -10327,12 +10323,12 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Ezra</t>
+          <t>Jeff</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Lombardo</t>
+          <t>Oulahen</t>
         </is>
       </c>
       <c r="C527" t="inlineStr"/>
@@ -10345,12 +10341,12 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Jeff</t>
+          <t>Jimmy</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Oulahen</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C528" t="inlineStr"/>
@@ -10363,12 +10359,12 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Jimmy</t>
+          <t>Reza</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Yu</t>
+          <t>Farahdel</t>
         </is>
       </c>
       <c r="C529" t="inlineStr"/>
@@ -10381,12 +10377,12 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>Reza</t>
+          <t>Eric</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Farahdel</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C530" t="inlineStr"/>
@@ -10399,7 +10395,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>Eric</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -10417,12 +10413,12 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Yonah</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Wasel</t>
         </is>
       </c>
       <c r="C532" t="inlineStr"/>
@@ -10435,12 +10431,12 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Yonah</t>
+          <t>Kayin</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Wasel</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C533" t="inlineStr"/>
@@ -10453,12 +10449,12 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Kayin</t>
+          <t>Megha</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Chandgothia</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
@@ -10471,12 +10467,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Megha</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Chandgothia</t>
+          <t>Friedman</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
@@ -10489,12 +10485,12 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Olivia</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>Friedman</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
@@ -10507,12 +10503,12 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Schein</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
@@ -10525,12 +10521,12 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Jayden</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>Schein</t>
+          <t>Xiao</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
@@ -10543,12 +10539,12 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>Jayden</t>
+          <t>Edward</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>Xiao</t>
+          <t>Min</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
@@ -10561,12 +10557,12 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Jing</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Min</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
@@ -10579,12 +10575,12 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>Jing</t>
+          <t>Lai Ming</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Kwan</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
@@ -10597,12 +10593,12 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Lai Ming</t>
+          <t>spencer</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>Kwan</t>
+          <t>abrams</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
@@ -10615,12 +10611,12 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>spencer</t>
+          <t>Fiona</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>abrams</t>
+          <t>Lam</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
@@ -10633,12 +10629,12 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Fiona</t>
+          <t>Liam</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Lam</t>
+          <t>Leibel</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
@@ -10651,12 +10647,12 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>John</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Leibel</t>
+          <t>Gow</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
@@ -10669,12 +10665,12 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>John</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Gow</t>
+          <t>Goldfarb</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
@@ -10687,12 +10683,12 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Vicky</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Goldfarb</t>
+          <t>Li</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
@@ -10705,12 +10701,12 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>Vicky</t>
+          <t>Gladice</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Li</t>
+          <t>Sarmiento</t>
         </is>
       </c>
       <c r="C548" t="inlineStr"/>
@@ -10723,12 +10719,12 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Gladice</t>
+          <t>Ginelle</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Sarmiento</t>
+          <t>Dacres</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
@@ -10741,12 +10737,12 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Ginelle</t>
+          <t>Asha</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Dacres</t>
+          <t>Raybardhan</t>
         </is>
       </c>
       <c r="C550" t="inlineStr"/>
@@ -10759,12 +10755,12 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Asha</t>
+          <t>harper</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Raybardhan</t>
+          <t>abrams</t>
         </is>
       </c>
       <c r="C551" t="inlineStr"/>
@@ -10777,12 +10773,12 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>harper</t>
+          <t>Thao</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>abrams</t>
+          <t>Nguyen</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
@@ -10795,12 +10791,12 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>Thao</t>
+          <t>Madeline</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>Nguyen</t>
+          <t>Arnone</t>
         </is>
       </c>
       <c r="C553" t="inlineStr"/>
@@ -10813,12 +10809,12 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Madeline</t>
+          <t>Patricio</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>Arnone</t>
+          <t>Dávalos ucha</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
@@ -10831,12 +10827,12 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Patricio</t>
+          <t>Doug</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Dávalos ucha</t>
+          <t>Tong</t>
         </is>
       </c>
       <c r="C555" t="inlineStr"/>
@@ -10849,12 +10845,12 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Doug</t>
+          <t>owen</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Tong</t>
+          <t>Stanley</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
@@ -10867,12 +10863,12 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>owen</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Stanley</t>
+          <t>Stavropoulos</t>
         </is>
       </c>
       <c r="C557" t="inlineStr"/>
@@ -10885,12 +10881,12 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>sam</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>Stavropoulos</t>
+          <t>Lombardo</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
@@ -10903,12 +10899,12 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>sam</t>
+          <t>Allyano</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Lombardo</t>
+          <t>Badrie-Deen</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
@@ -10921,12 +10917,12 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Allyano</t>
+          <t>Griffin</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Badrie-Deen</t>
+          <t>Levy</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
@@ -10939,12 +10935,12 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Griffin</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Levy</t>
+          <t>Dai</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
@@ -10957,12 +10953,12 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Stephen</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Dai</t>
+          <t>Fraser</t>
         </is>
       </c>
       <c r="C562" t="inlineStr"/>
@@ -10975,12 +10971,12 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>Stephen</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Fraser</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
@@ -10993,12 +10989,12 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Krish</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>Kaufman</t>
+          <t>Raybardhan</t>
         </is>
       </c>
       <c r="C564" t="inlineStr"/>
@@ -11011,12 +11007,12 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>Krish</t>
+          <t>Rhea</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Raybardhan</t>
+          <t>Chandgothia</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
@@ -11029,12 +11025,12 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Rhea</t>
+          <t>Scarlett</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Chandgothia</t>
+          <t>Trinh</t>
         </is>
       </c>
       <c r="C566" t="inlineStr"/>
@@ -11047,12 +11043,12 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>Scarlett</t>
+          <t>yaffa</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Trinh</t>
+          <t>Wasel</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
@@ -11065,12 +11061,12 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>yaffa</t>
+          <t>Riley</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>Wasel</t>
+          <t>Eisen</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
@@ -11083,12 +11079,12 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Riley</t>
+          <t>Yuchen</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Eisen</t>
+          <t>Wang</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
@@ -11101,12 +11097,12 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Yuchen</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>Wang</t>
+          <t>Sukadil</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
@@ -11119,12 +11115,12 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Neal</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Sukadil</t>
+          <t>Arora</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
@@ -11137,12 +11133,12 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Neal</t>
+          <t>Caleigh</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Arora</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C572" t="inlineStr"/>
@@ -11155,12 +11151,12 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>Caleigh</t>
+          <t>Simom</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Chan</t>
+          <t>Yum</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
@@ -11173,12 +11169,12 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>Simom</t>
+          <t>Claire</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>Yum</t>
+          <t>Oulahen</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
@@ -11191,12 +11187,12 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>Claire</t>
+          <t>Kelly</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Oulahen</t>
+          <t>Lin</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
@@ -11209,12 +11205,12 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>Kelly</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>Lin</t>
+          <t>Tushinski</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
@@ -11227,12 +11223,12 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Max</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Tushinski</t>
+          <t>ZHU</t>
         </is>
       </c>
       <c r="C577" t="inlineStr"/>
@@ -11245,12 +11241,12 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>Max</t>
+          <t>Aileen</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>ZHU</t>
+          <t>Huang</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
@@ -11263,12 +11259,12 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>Aileen</t>
+          <t>Lyss</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Huang</t>
+          <t>Arde</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
@@ -11281,7 +11277,7 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>Lyss</t>
+          <t>Cris</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -11299,7 +11295,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Cris</t>
+          <t>Ev</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -11317,15 +11313,19 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Ev</t>
+          <t>Shereen</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>Arde</t>
-        </is>
-      </c>
-      <c r="C582" t="inlineStr"/>
+          <t>Opiana</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>shereenkateopiana@gmail.com</t>
+        </is>
+      </c>
       <c r="D582" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11335,19 +11335,15 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Shereen</t>
+          <t>Henrietta</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Opiana</t>
-        </is>
-      </c>
-      <c r="C583" t="inlineStr">
-        <is>
-          <t>shereenkateopiana@gmail.com</t>
-        </is>
-      </c>
+          <t>Tsui</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11357,12 +11353,12 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Henrietta</t>
+          <t>Melanie</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Tsui</t>
+          <t>Simunovic</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
@@ -11375,12 +11371,12 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Melanie</t>
+          <t>Henry</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Simunovic</t>
+          <t>Yu</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
@@ -11393,15 +11389,19 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Henry</t>
+          <t>Ernie</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Yu</t>
-        </is>
-      </c>
-      <c r="C586" t="inlineStr"/>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>ernie.douglas@intact.net</t>
+        </is>
+      </c>
       <c r="D586" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11411,19 +11411,15 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>Ernie</t>
+          <t>ANDREW</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Douglas</t>
-        </is>
-      </c>
-      <c r="C587" t="inlineStr">
-        <is>
-          <t>ernie.douglas@intact.net</t>
-        </is>
-      </c>
+          <t>NGUYEN</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11433,12 +11429,12 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>ANDREW</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>NGUYEN</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
@@ -11451,12 +11447,12 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Khalil</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>R</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
@@ -11469,12 +11465,12 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Khalil</t>
+          <t>Hailey</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Liem</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
@@ -11487,12 +11483,12 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>Hailey</t>
+          <t>Erin</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Liem</t>
+          <t>Birman</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
@@ -11505,15 +11501,19 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>Erin</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Birman</t>
-        </is>
-      </c>
-      <c r="C592" t="inlineStr"/>
+          <t>Yang</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>chrisabrina2021@gmail.com</t>
+        </is>
+      </c>
       <c r="D592" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11523,19 +11523,15 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Kaitlyn</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Yang</t>
-        </is>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>chrisabrina2021@gmail.com</t>
-        </is>
-      </c>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11545,12 +11541,12 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>Kaitlyn</t>
+          <t>Rowena</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>Ballesteros</t>
         </is>
       </c>
       <c r="C594" t="inlineStr"/>
@@ -11563,15 +11559,19 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Rowena</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Ballesteros</t>
-        </is>
-      </c>
-      <c r="C595" t="inlineStr"/>
+          <t>Forostyanko</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>alexforostyanlo30@gmail.com</t>
+        </is>
+      </c>
       <c r="D595" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11581,19 +11581,15 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Rose Ann</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Forostyanko</t>
-        </is>
-      </c>
-      <c r="C596" t="inlineStr">
-        <is>
-          <t>alexforostyanlo30@gmail.com</t>
-        </is>
-      </c>
+          <t>Claveria</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11603,15 +11599,19 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Rose Ann</t>
+          <t>Roni</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Claveria</t>
-        </is>
-      </c>
-      <c r="C597" t="inlineStr"/>
+          <t>Macmull</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>cuball3zen@gmail.com</t>
+        </is>
+      </c>
       <c r="D597" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11621,19 +11621,15 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Roni</t>
+          <t>Kathleen</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Macmull</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr">
-        <is>
-          <t>cuball3zen@gmail.com</t>
-        </is>
-      </c>
+          <t>Nadon</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr"/>
       <c r="D598" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11643,12 +11639,12 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>Kathleen</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Render</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
@@ -11661,12 +11657,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>Render</t>
+          <t>Nadon</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
@@ -11679,12 +11675,12 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Evan</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Nadon</t>
+          <t>Kean</t>
         </is>
       </c>
       <c r="C601" t="inlineStr"/>
@@ -11697,7 +11693,7 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>Evan</t>
+          <t>Lauren</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -11715,12 +11711,12 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>Lauren</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Kean</t>
+          <t>Luk</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
@@ -11733,7 +11729,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Samuel</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -11751,15 +11747,19 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>Samuel</t>
+          <t>Ervie</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Luk</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr"/>
+          <t>Kae Garcia</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>ervie@amlb.ca</t>
+        </is>
+      </c>
       <c r="D605" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11769,19 +11769,15 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>Ervie</t>
+          <t>Jaxon</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Kae Garcia</t>
-        </is>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>ervie@amlb.ca</t>
-        </is>
-      </c>
+          <t>Liem</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11791,7 +11787,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Jaxon</t>
+          <t>Hannah</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -11809,12 +11805,12 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Hannah</t>
+          <t>Lea</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Liem</t>
+          <t>Dungao</t>
         </is>
       </c>
       <c r="C608" t="inlineStr"/>
@@ -11827,12 +11823,12 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>Lea</t>
+          <t>Gemma</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Dungao</t>
+          <t>Pham</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
@@ -11845,12 +11841,12 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Mark</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Pham</t>
+          <t>Karam</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
@@ -11863,12 +11859,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>Mark</t>
+          <t>Melania</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Karam</t>
+          <t>Mendoza</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
@@ -11881,12 +11877,12 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>Melania</t>
+          <t>Malek</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Mendoza</t>
+          <t>Sakka</t>
         </is>
       </c>
       <c r="C612" t="inlineStr"/>
@@ -11899,12 +11895,12 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Malek</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Sakka</t>
+          <t>Tan</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
@@ -11917,15 +11913,19 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Vanessa</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
         <is>
-          <t>Tan</t>
-        </is>
-      </c>
-      <c r="C614" t="inlineStr"/>
+          <t>Infanti</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>vanessa.infanti@hotmail.com</t>
+        </is>
+      </c>
       <c r="D614" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11935,19 +11935,15 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Vanessa</t>
+          <t>Noah</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>Infanti</t>
-        </is>
-      </c>
-      <c r="C615" t="inlineStr">
-        <is>
-          <t>vanessa.infanti@hotmail.com</t>
-        </is>
-      </c>
+          <t>Nepomuceno</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11957,15 +11953,19 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Josh</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Nepomuceno</t>
-        </is>
-      </c>
-      <c r="C616" t="inlineStr"/>
+          <t>Samuels</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>joshsamuels04@gmail.com</t>
+        </is>
+      </c>
       <c r="D616" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11975,19 +11975,15 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Josh</t>
+          <t>Jisoo</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Samuels</t>
-        </is>
-      </c>
-      <c r="C617" t="inlineStr">
-        <is>
-          <t>joshsamuels04@gmail.com</t>
-        </is>
-      </c>
+          <t>Maynard</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -11997,12 +11993,12 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>Jisoo</t>
+          <t>Sabrina</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Maynard</t>
+          <t>Cristiano</t>
         </is>
       </c>
       <c r="C618" t="inlineStr"/>
@@ -12015,15 +12011,19 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>Sabrina</t>
+          <t>Steven</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
         <is>
-          <t>Cristiano</t>
-        </is>
-      </c>
-      <c r="C619" t="inlineStr"/>
+          <t>Ding</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>steven.ding@mail.utoronto.ca</t>
+        </is>
+      </c>
       <c r="D619" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12033,17 +12033,17 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>Steven</t>
+          <t>Winnie</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>Ding</t>
+          <t>Chan</t>
         </is>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>steven.ding@mail.utoronto.ca</t>
+          <t>wcmchen125@gmail.com</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -12055,19 +12055,15 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Winnie</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>Chan</t>
-        </is>
-      </c>
-      <c r="C621" t="inlineStr">
-        <is>
-          <t>wcmchen125@gmail.com</t>
-        </is>
-      </c>
+          <t>Cheng</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12077,12 +12073,12 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Blendi</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>Cheng</t>
+          <t>Collaku</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
@@ -12095,12 +12091,12 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Blendi</t>
+          <t>Brandon</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Collaku</t>
+          <t>Chin</t>
         </is>
       </c>
       <c r="C623" t="inlineStr"/>
@@ -12113,15 +12109,19 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Brandon</t>
+          <t>Ernie</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Chin</t>
-        </is>
-      </c>
-      <c r="C624" t="inlineStr"/>
+          <t>Douglas</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>kirby.chan19@gmail.com</t>
+        </is>
+      </c>
       <c r="D624" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12131,17 +12131,17 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>Ernie</t>
+          <t>Natalie</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>Douglas</t>
+          <t>Chiu</t>
         </is>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>kirby.chan19@gmail.com</t>
+          <t>natalien+pickle@gmail.com</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -12153,19 +12153,15 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Natalie</t>
+          <t>Ian W</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Chiu</t>
-        </is>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>natalien+pickle@gmail.com</t>
-        </is>
-      </c>
+          <t>Chow</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12175,12 +12171,12 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Ian W</t>
+          <t>Cyrene</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>Chow</t>
+          <t>Pamo</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
@@ -12193,7 +12189,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Cyrene</t>
+          <t>Caitlyn</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -12211,12 +12207,12 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Caitlyn</t>
+          <t>Amie</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>Pamo</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="C629" t="inlineStr"/>
@@ -12247,12 +12243,12 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>Amie</t>
+          <t>Houston</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Cheng</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
@@ -12265,12 +12261,12 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>Houston</t>
+          <t>Ana</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>Cheng</t>
+          <t>Folletet</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
@@ -12283,12 +12279,12 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>Ana</t>
+          <t>Howard</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Folletet</t>
+          <t>Liquornik</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
@@ -12301,12 +12297,12 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>Howard</t>
+          <t>Angelina</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
         <is>
-          <t>Liquornik</t>
+          <t>Meng</t>
         </is>
       </c>
       <c r="C634" t="inlineStr"/>
@@ -12319,12 +12315,12 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>Angelina</t>
+          <t>Andrew</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>Meng</t>
+          <t>Wun</t>
         </is>
       </c>
       <c r="C635" t="inlineStr"/>
@@ -12337,12 +12333,12 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>Andrew</t>
+          <t>Katie</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>Wun</t>
+          <t>Parat</t>
         </is>
       </c>
       <c r="C636" t="inlineStr"/>
@@ -12355,12 +12351,12 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Katie</t>
+          <t>Dov</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>Parat</t>
+          <t>Atlin</t>
         </is>
       </c>
       <c r="C637" t="inlineStr"/>
@@ -12373,12 +12369,12 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>Dov</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>Atlin</t>
+          <t>Mandell</t>
         </is>
       </c>
       <c r="C638" t="inlineStr"/>
@@ -12391,12 +12387,12 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Issy</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>Mandell</t>
+          <t>Carey</t>
         </is>
       </c>
       <c r="C639" t="inlineStr"/>
@@ -12409,12 +12405,12 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>Issy</t>
+          <t>Sarah</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>Carey</t>
+          <t>Empey</t>
         </is>
       </c>
       <c r="C640" t="inlineStr"/>
@@ -12427,12 +12423,12 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>Sarah</t>
+          <t>Kaylee</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>Empey</t>
+          <t>Segal</t>
         </is>
       </c>
       <c r="C641" t="inlineStr"/>
@@ -12445,12 +12441,12 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Kaylee</t>
+          <t>Sebastien</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>Segal</t>
+          <t>Brice</t>
         </is>
       </c>
       <c r="C642" t="inlineStr"/>
@@ -12463,7 +12459,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>Sebastien</t>
+          <t>Andre</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -12481,12 +12477,12 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>Andre</t>
+          <t>Rylan</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>Brice</t>
+          <t>Atlin</t>
         </is>
       </c>
       <c r="C644" t="inlineStr"/>
@@ -12499,12 +12495,12 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>Rylan</t>
+          <t>Gabi</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>Atlin</t>
+          <t>Moad</t>
         </is>
       </c>
       <c r="C645" t="inlineStr"/>
@@ -12517,15 +12513,19 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>Gabi</t>
+          <t>Brooke</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>Moad</t>
-        </is>
-      </c>
-      <c r="C646" t="inlineStr"/>
+          <t>Mandell</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>bmandell@havergal.on.ca</t>
+        </is>
+      </c>
       <c r="D646" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12535,19 +12535,15 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Brooke</t>
+          <t>Scarlett</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>Mandell</t>
-        </is>
-      </c>
-      <c r="C647" t="inlineStr">
-        <is>
-          <t>bmandell@havergal.on.ca</t>
-        </is>
-      </c>
+          <t>Brice</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr"/>
       <c r="D647" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12557,12 +12553,12 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Scarlett</t>
+          <t>Shayne</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>Brice</t>
+          <t>Atlin</t>
         </is>
       </c>
       <c r="C648" t="inlineStr"/>
@@ -12575,12 +12571,12 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Shayne</t>
+          <t>Runa</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>Atlin</t>
+          <t>Saito</t>
         </is>
       </c>
       <c r="C649" t="inlineStr"/>
@@ -12593,12 +12589,12 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Runa</t>
+          <t>Dana</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>Saito</t>
+          <t>Ma</t>
         </is>
       </c>
       <c r="C650" t="inlineStr"/>
@@ -12611,12 +12607,12 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Dana</t>
+          <t>April</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>Ma</t>
+          <t>Dysart</t>
         </is>
       </c>
       <c r="C651" t="inlineStr"/>
@@ -12629,12 +12625,12 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>April</t>
+          <t>Whitney</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>Dysart</t>
+          <t>Cathcart</t>
         </is>
       </c>
       <c r="C652" t="inlineStr"/>
@@ -12647,7 +12643,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>Whitney</t>
+          <t>Addison</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -12665,12 +12661,12 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>Addison</t>
+          <t>Molly</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
         <is>
-          <t>Cathcart</t>
+          <t>Hayhurst</t>
         </is>
       </c>
       <c r="C654" t="inlineStr"/>
@@ -12683,12 +12679,12 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>Molly</t>
+          <t>Bruce</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
         <is>
-          <t>Hayhurst</t>
+          <t>Cathcart</t>
         </is>
       </c>
       <c r="C655" t="inlineStr"/>
@@ -12701,12 +12697,12 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>Bruce</t>
+          <t>Serena</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Cathcart</t>
+          <t>Woodley</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
@@ -12719,15 +12715,19 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Serena</t>
+          <t>Fry</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>Woodley</t>
-        </is>
-      </c>
-      <c r="C657" t="inlineStr"/>
+          <t>Kreps</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>fryemupgaming@gmail.com</t>
+        </is>
+      </c>
       <c r="D657" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12737,17 +12737,17 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>Fry</t>
+          <t>Yunchang</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>Kreps</t>
+          <t>Gao</t>
         </is>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>fryemupgaming@gmail.com</t>
+          <t>gaoyunchang0905@gmail.com</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -12759,19 +12759,15 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Yunchang</t>
+          <t>Trudy</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>Gao</t>
-        </is>
-      </c>
-      <c r="C659" t="inlineStr">
-        <is>
-          <t>gaoyunchang0905@gmail.com</t>
-        </is>
-      </c>
+          <t>Tan</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12781,12 +12777,12 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>Trudy</t>
+          <t>Jason</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>Tan</t>
+          <t>Kim</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
@@ -12799,12 +12795,12 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Jason</t>
+          <t>Ava</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>Kim</t>
+          <t>blacker</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
@@ -12817,12 +12813,12 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Alvina</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
         <is>
-          <t>blacker</t>
+          <t>Tam</t>
         </is>
       </c>
       <c r="C662" t="inlineStr"/>
@@ -12835,15 +12831,19 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>Alvina</t>
+          <t>Anthony</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>Tam</t>
-        </is>
-      </c>
-      <c r="C663" t="inlineStr"/>
+          <t>Theuma</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>anthontflash275@hotmail.com</t>
+        </is>
+      </c>
       <c r="D663" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12853,17 +12853,17 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>Anthony</t>
+          <t>Terry</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>Theuma</t>
+          <t>Carr</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>anthontflash275@hotmail.com</t>
+          <t>ticonc680@gmail.com</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -12875,19 +12875,15 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>Terry</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
         <is>
-          <t>Carr</t>
-        </is>
-      </c>
-      <c r="C665" t="inlineStr">
-        <is>
-          <t>ticonc680@gmail.com</t>
-        </is>
-      </c>
+          <t>Nguyen</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr"/>
       <c r="D665" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12897,15 +12893,19 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Pamela</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
         <is>
-          <t>Nguyen</t>
-        </is>
-      </c>
-      <c r="C666" t="inlineStr"/>
+          <t>MCRAE</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>genieno1.pvc@gmail.com</t>
+        </is>
+      </c>
       <c r="D666" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12915,19 +12915,15 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Pamela</t>
+          <t>Mike</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>MCRAE</t>
-        </is>
-      </c>
-      <c r="C667" t="inlineStr">
-        <is>
-          <t>genieno1.pvc@gmail.com</t>
-        </is>
-      </c>
+          <t>Wong</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr"/>
       <c r="D667" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
@@ -12937,12 +12933,12 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>Mike</t>
+          <t>Justin</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>Wong</t>
+          <t>Feng</t>
         </is>
       </c>
       <c r="C668" t="inlineStr"/>
@@ -12955,12 +12951,12 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Justin</t>
+          <t>Ma Siobhan</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>Feng</t>
+          <t>Valenzuela</t>
         </is>
       </c>
       <c r="C669" t="inlineStr"/>
@@ -12973,7 +12969,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Ma Siobhan</t>
+          <t>Vaughn</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -12991,7 +12987,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>Vaughn</t>
+          <t>Yves Lorenz</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -13009,7 +13005,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Yves Lorenz</t>
+          <t>Lorenz</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -13019,24 +13015,6 @@
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr">
-        <is>
-          <t>downsview@pickleplex.ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>Lorenz</t>
-        </is>
-      </c>
-      <c r="B673" t="inlineStr">
-        <is>
-          <t>Valenzuela</t>
-        </is>
-      </c>
-      <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr">
         <is>
           <t>downsview@pickleplex.ca</t>
         </is>
